--- a/outputs/portfolio_combined/performance_from_tsfm.xlsx
+++ b/outputs/portfolio_combined/performance_from_tsfm.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-2499.999999999999</v>
+        <v>-2500</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -487,19 +487,19 @@
         <v>45985</v>
       </c>
       <c r="B3" t="n">
-        <v>2499.015001444528</v>
+        <v>2509.241784185071</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9849985554724299</v>
+        <v>9.241784185070628</v>
       </c>
       <c r="D3" t="n">
-        <v>-2530.499918876664</v>
+        <v>-2507.516821264939</v>
       </c>
       <c r="E3" t="n">
-        <v>-30.49991887666465</v>
+        <v>-7.516821264939153</v>
       </c>
       <c r="F3" t="n">
-        <v>-31.48491743213708</v>
+        <v>1.724962920131475</v>
       </c>
     </row>
     <row r="4">
@@ -507,19 +507,19 @@
         <v>45986</v>
       </c>
       <c r="B4" t="n">
-        <v>2523.706074043022</v>
+        <v>2519.873137277009</v>
       </c>
       <c r="C4" t="n">
-        <v>24.69107259849488</v>
+        <v>10.63135309193831</v>
       </c>
       <c r="D4" t="n">
-        <v>-2564.642119656648</v>
+        <v>-2529.902132418876</v>
       </c>
       <c r="E4" t="n">
-        <v>-34.14220077998471</v>
+        <v>-22.38531115393653</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.451128181489821</v>
+        <v>-11.75395806199822</v>
       </c>
     </row>
     <row r="5">
@@ -527,19 +527,19 @@
         <v>45987</v>
       </c>
       <c r="B5" t="n">
-        <v>2527.819191632828</v>
+        <v>2546.722925129732</v>
       </c>
       <c r="C5" t="n">
-        <v>4.113117589805825</v>
+        <v>26.84978785272324</v>
       </c>
       <c r="D5" t="n">
-        <v>-2600.925037513096</v>
+        <v>-2544.628592397829</v>
       </c>
       <c r="E5" t="n">
-        <v>-36.28291785644751</v>
+        <v>-14.7264599789537</v>
       </c>
       <c r="F5" t="n">
-        <v>-32.16980026664169</v>
+        <v>12.12332787376954</v>
       </c>
     </row>
     <row r="6">
@@ -547,19 +547,19 @@
         <v>45988</v>
       </c>
       <c r="B6" t="n">
-        <v>2551.312923578854</v>
+        <v>2558.224911854697</v>
       </c>
       <c r="C6" t="n">
-        <v>23.49373194602549</v>
+        <v>11.50198672496526</v>
       </c>
       <c r="D6" t="n">
-        <v>-2595.232705985193</v>
+        <v>-2546.795363459509</v>
       </c>
       <c r="E6" t="n">
-        <v>5.692331527903207</v>
+        <v>-2.166771061679356</v>
       </c>
       <c r="F6" t="n">
-        <v>29.1860634739287</v>
+        <v>9.335215663285908</v>
       </c>
     </row>
     <row r="7">
@@ -567,19 +567,19 @@
         <v>45989</v>
       </c>
       <c r="B7" t="n">
-        <v>2532.011309333894</v>
+        <v>2550.997485404009</v>
       </c>
       <c r="C7" t="n">
-        <v>-19.30161424495964</v>
+        <v>-7.227426450688654</v>
       </c>
       <c r="D7" t="n">
-        <v>-2601.70624179691</v>
+        <v>-2551.32509226679</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.473535811716829</v>
+        <v>-4.529728807281572</v>
       </c>
       <c r="F7" t="n">
-        <v>-25.77515005667647</v>
+        <v>-11.75715525797023</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +587,19 @@
         <v>45992</v>
       </c>
       <c r="B8" t="n">
-        <v>2487.261678378264</v>
+        <v>2523.073916685363</v>
       </c>
       <c r="C8" t="n">
-        <v>-44.74963095562998</v>
+        <v>-27.92356871864558</v>
       </c>
       <c r="D8" t="n">
-        <v>-2590.259160668065</v>
+        <v>-2547.995302909327</v>
       </c>
       <c r="E8" t="n">
-        <v>11.44708112884427</v>
+        <v>3.329789357463142</v>
       </c>
       <c r="F8" t="n">
-        <v>-33.30254982678571</v>
+        <v>-24.59377936118244</v>
       </c>
     </row>
     <row r="9">
@@ -607,19 +607,19 @@
         <v>45993</v>
       </c>
       <c r="B9" t="n">
-        <v>2489.337994257454</v>
+        <v>2519.033189160617</v>
       </c>
       <c r="C9" t="n">
-        <v>2.076315879189679</v>
+        <v>-4.040727524746671</v>
       </c>
       <c r="D9" t="n">
-        <v>-2583.753941184441</v>
+        <v>-2538.411019701274</v>
       </c>
       <c r="E9" t="n">
-        <v>6.505219483623932</v>
+        <v>9.584283208053421</v>
       </c>
       <c r="F9" t="n">
-        <v>8.581535362813611</v>
+        <v>5.543555683306749</v>
       </c>
     </row>
     <row r="10">
@@ -627,19 +627,19 @@
         <v>45994</v>
       </c>
       <c r="B10" t="n">
-        <v>2502.798106627241</v>
+        <v>2514.062654748563</v>
       </c>
       <c r="C10" t="n">
-        <v>13.46011236978711</v>
+        <v>-4.970534412053439</v>
       </c>
       <c r="D10" t="n">
-        <v>-2572.29013283914</v>
+        <v>-2530.102778725055</v>
       </c>
       <c r="E10" t="n">
-        <v>11.46380834530146</v>
+        <v>8.308240976218258</v>
       </c>
       <c r="F10" t="n">
-        <v>24.92392071508857</v>
+        <v>3.337706564164819</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         <v>45995</v>
       </c>
       <c r="B11" t="n">
-        <v>2530.507615272473</v>
+        <v>2530.330151075031</v>
       </c>
       <c r="C11" t="n">
-        <v>27.70950864523184</v>
+        <v>16.26749632646761</v>
       </c>
       <c r="D11" t="n">
-        <v>-2601.64180892154</v>
+        <v>-2539.207574917416</v>
       </c>
       <c r="E11" t="n">
-        <v>-29.35167608240045</v>
+        <v>-9.104796192360027</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.642167437168609</v>
+        <v>7.162700134107581</v>
       </c>
     </row>
     <row r="12">
@@ -667,19 +667,19 @@
         <v>45996</v>
       </c>
       <c r="B12" t="n">
-        <v>2533.189238113629</v>
+        <v>2548.186615865847</v>
       </c>
       <c r="C12" t="n">
-        <v>2.681622841156695</v>
+        <v>17.85646479081652</v>
       </c>
       <c r="D12" t="n">
-        <v>-2592.274917662057</v>
+        <v>-2534.627561346466</v>
       </c>
       <c r="E12" t="n">
-        <v>9.366891259483509</v>
+        <v>4.580013570949177</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0485141006402</v>
+        <v>22.43647836176569</v>
       </c>
     </row>
     <row r="13">
@@ -687,19 +687,19 @@
         <v>45999</v>
       </c>
       <c r="B13" t="n">
-        <v>2541.080447844903</v>
+        <v>2560.748857919597</v>
       </c>
       <c r="C13" t="n">
-        <v>7.891209731273648</v>
+        <v>12.56224205374974</v>
       </c>
       <c r="D13" t="n">
-        <v>-2600.25628516144</v>
+        <v>-2520.549351124554</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.981367499383396</v>
+        <v>14.07821022191274</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.09015776810974785</v>
+        <v>26.64045227566248</v>
       </c>
     </row>
     <row r="14">
@@ -707,19 +707,19 @@
         <v>46000</v>
       </c>
       <c r="B14" t="n">
-        <v>2564.979412852995</v>
+        <v>2560.674870301209</v>
       </c>
       <c r="C14" t="n">
-        <v>23.89896500809209</v>
+        <v>-0.07398761838749124</v>
       </c>
       <c r="D14" t="n">
-        <v>-2598.23916988402</v>
+        <v>-2520.248484463686</v>
       </c>
       <c r="E14" t="n">
-        <v>2.017115277420544</v>
+        <v>0.300866660867996</v>
       </c>
       <c r="F14" t="n">
-        <v>25.91608028551263</v>
+        <v>0.2268790424805047</v>
       </c>
     </row>
     <row r="15">
@@ -727,19 +727,19 @@
         <v>46001</v>
       </c>
       <c r="B15" t="n">
-        <v>2575.315307458719</v>
+        <v>2570.035548179049</v>
       </c>
       <c r="C15" t="n">
-        <v>10.33589460572375</v>
+        <v>9.360677877839862</v>
       </c>
       <c r="D15" t="n">
-        <v>-2606.363308202407</v>
+        <v>-2522.843232685599</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.124138318387395</v>
+        <v>-2.594748221913505</v>
       </c>
       <c r="F15" t="n">
-        <v>2.211756287336357</v>
+        <v>6.765929655926357</v>
       </c>
     </row>
     <row r="16">
@@ -747,19 +747,19 @@
         <v>46002</v>
       </c>
       <c r="B16" t="n">
-        <v>2578.035359413948</v>
+        <v>2568.960895568924</v>
       </c>
       <c r="C16" t="n">
-        <v>2.720051955228882</v>
+        <v>-1.074652610125213</v>
       </c>
       <c r="D16" t="n">
-        <v>-2623.443966876085</v>
+        <v>-2529.923611836493</v>
       </c>
       <c r="E16" t="n">
-        <v>-17.08065867367804</v>
+        <v>-7.080379150893805</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.36060671844916</v>
+        <v>-8.155031761019018</v>
       </c>
     </row>
     <row r="17">
@@ -767,19 +767,19 @@
         <v>46003</v>
       </c>
       <c r="B17" t="n">
-        <v>2572.751993671528</v>
+        <v>2570.858119711815</v>
       </c>
       <c r="C17" t="n">
-        <v>-5.283365742419392</v>
+        <v>1.897224142890536</v>
       </c>
       <c r="D17" t="n">
-        <v>-2629.781866229474</v>
+        <v>-2530.6890668741</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.337899353389275</v>
+        <v>-0.765455037607353</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.62126509580867</v>
+        <v>1.131769105283183</v>
       </c>
     </row>
     <row r="18">
@@ -787,19 +787,19 @@
         <v>46006</v>
       </c>
       <c r="B18" t="n">
-        <v>2571.179185430816</v>
+        <v>2581.418348836035</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.57280824071222</v>
+        <v>10.56022912422077</v>
       </c>
       <c r="D18" t="n">
-        <v>-2653.908404156962</v>
+        <v>-2551.154891365105</v>
       </c>
       <c r="E18" t="n">
-        <v>-24.12653792748733</v>
+        <v>-20.46582449100424</v>
       </c>
       <c r="F18" t="n">
-        <v>-25.69934616819955</v>
+        <v>-9.905595366783473</v>
       </c>
     </row>
     <row r="19">
@@ -807,19 +807,19 @@
         <v>46007</v>
       </c>
       <c r="B19" t="n">
-        <v>2558.900773454625</v>
+        <v>2568.136559247375</v>
       </c>
       <c r="C19" t="n">
-        <v>-12.27841197619136</v>
+        <v>-13.28178958866056</v>
       </c>
       <c r="D19" t="n">
-        <v>-2635.780834923354</v>
+        <v>-2534.337921000345</v>
       </c>
       <c r="E19" t="n">
-        <v>18.12756923360803</v>
+        <v>16.81697036475907</v>
       </c>
       <c r="F19" t="n">
-        <v>5.849157257416664</v>
+        <v>3.535180776098514</v>
       </c>
     </row>
     <row r="20">
@@ -827,19 +827,19 @@
         <v>46008</v>
       </c>
       <c r="B20" t="n">
-        <v>2575.508466349103</v>
+        <v>2570.440799823549</v>
       </c>
       <c r="C20" t="n">
-        <v>16.60769289447808</v>
+        <v>2.304240576173925</v>
       </c>
       <c r="D20" t="n">
-        <v>-2617.936645738696</v>
+        <v>-2557.222734776123</v>
       </c>
       <c r="E20" t="n">
-        <v>17.84418918465781</v>
+        <v>-22.88481377577773</v>
       </c>
       <c r="F20" t="n">
-        <v>34.45188207913588</v>
+        <v>-20.5805731996038</v>
       </c>
     </row>
     <row r="21">
@@ -847,19 +847,19 @@
         <v>46009</v>
       </c>
       <c r="B21" t="n">
-        <v>2613.554147293501</v>
+        <v>2584.123791088713</v>
       </c>
       <c r="C21" t="n">
-        <v>38.04568094439765</v>
+        <v>13.68299126516467</v>
       </c>
       <c r="D21" t="n">
-        <v>-2646.415172985178</v>
+        <v>-2576.475156238495</v>
       </c>
       <c r="E21" t="n">
-        <v>-28.47852724648237</v>
+        <v>-19.25242146237179</v>
       </c>
       <c r="F21" t="n">
-        <v>9.567153697915273</v>
+        <v>-5.569430197207112</v>
       </c>
     </row>
     <row r="22">
@@ -867,19 +867,19 @@
         <v>46010</v>
       </c>
       <c r="B22" t="n">
-        <v>2668.426764372464</v>
+        <v>2609.50958098776</v>
       </c>
       <c r="C22" t="n">
-        <v>54.87261707896369</v>
+        <v>25.38578989904681</v>
       </c>
       <c r="D22" t="n">
-        <v>-2642.246133861868</v>
+        <v>-2587.042982613463</v>
       </c>
       <c r="E22" t="n">
-        <v>4.16903912331054</v>
+        <v>-10.56782637496781</v>
       </c>
       <c r="F22" t="n">
-        <v>59.04165620227423</v>
+        <v>14.817963524079</v>
       </c>
     </row>
     <row r="23">
@@ -887,19 +887,19 @@
         <v>46013</v>
       </c>
       <c r="B23" t="n">
-        <v>2674.341845475152</v>
+        <v>2621.509149529658</v>
       </c>
       <c r="C23" t="n">
-        <v>5.915081102687964</v>
+        <v>11.99956854189759</v>
       </c>
       <c r="D23" t="n">
-        <v>-2634.001740600025</v>
+        <v>-2583.780516048416</v>
       </c>
       <c r="E23" t="n">
-        <v>8.244393261843015</v>
+        <v>3.262466565046907</v>
       </c>
       <c r="F23" t="n">
-        <v>14.15947436453098</v>
+        <v>15.2620351069445</v>
       </c>
     </row>
     <row r="24">
@@ -907,19 +907,19 @@
         <v>46014</v>
       </c>
       <c r="B24" t="n">
-        <v>2669.5662097597</v>
+        <v>2622.000856497647</v>
       </c>
       <c r="C24" t="n">
-        <v>-4.775635715452609</v>
+        <v>0.4917069679895576</v>
       </c>
       <c r="D24" t="n">
-        <v>-2633.686560881034</v>
+        <v>-2583.987697159314</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3151797189912031</v>
+        <v>-0.207181110898091</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.460455996461405</v>
+        <v>0.2845258570914666</v>
       </c>
     </row>
     <row r="25">
@@ -927,19 +927,19 @@
         <v>46015</v>
       </c>
       <c r="B25" t="n">
-        <v>2664.587945523367</v>
+        <v>2619.995496820166</v>
       </c>
       <c r="C25" t="n">
-        <v>-4.978264236332961</v>
+        <v>-2.00535967748101</v>
       </c>
       <c r="D25" t="n">
-        <v>-2567.836755030836</v>
+        <v>-2691.079974720727</v>
       </c>
       <c r="E25" t="n">
-        <v>65.84980585019775</v>
+        <v>-107.0922775614126</v>
       </c>
       <c r="F25" t="n">
-        <v>60.87154161386479</v>
+        <v>-109.0976372388936</v>
       </c>
     </row>
     <row r="26">
@@ -947,19 +947,19 @@
         <v>46020</v>
       </c>
       <c r="B26" t="n">
-        <v>2677.495916645338</v>
+        <v>2633.549187445756</v>
       </c>
       <c r="C26" t="n">
-        <v>12.90797112197151</v>
+        <v>13.5536906255893</v>
       </c>
       <c r="D26" t="n">
-        <v>-2653.342584681595</v>
+        <v>-2559.262291399675</v>
       </c>
       <c r="E26" t="n">
-        <v>-85.5058296507591</v>
+        <v>131.8176833210514</v>
       </c>
       <c r="F26" t="n">
-        <v>-72.59785852878758</v>
+        <v>145.3713739466407</v>
       </c>
     </row>
     <row r="27">
@@ -967,19 +967,19 @@
         <v>46021</v>
       </c>
       <c r="B27" t="n">
-        <v>2716.521210553601</v>
+        <v>2656.129557607249</v>
       </c>
       <c r="C27" t="n">
-        <v>39.02529390826248</v>
+        <v>22.58037016149365</v>
       </c>
       <c r="D27" t="n">
-        <v>-2660.442173108304</v>
+        <v>-2586.429489979063</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.099588426709033</v>
+        <v>-27.16719857938779</v>
       </c>
       <c r="F27" t="n">
-        <v>31.92570548155345</v>
+        <v>-4.586828417894139</v>
       </c>
     </row>
     <row r="28">
@@ -987,19 +987,19 @@
         <v>46022</v>
       </c>
       <c r="B28" t="n">
-        <v>2716.521210553601</v>
+        <v>2655.053164570672</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-1.076393036577429</v>
       </c>
       <c r="D28" t="n">
-        <v>-2570.916798896622</v>
+        <v>-2701.592827158996</v>
       </c>
       <c r="E28" t="n">
-        <v>89.52537421168199</v>
+        <v>-115.163337179933</v>
       </c>
       <c r="F28" t="n">
-        <v>89.52537421168199</v>
+        <v>-116.2397302165105</v>
       </c>
     </row>
     <row r="29">
@@ -1007,19 +1007,19 @@
         <v>46024</v>
       </c>
       <c r="B29" t="n">
-        <v>2746.257303514555</v>
+        <v>2650.347888074429</v>
       </c>
       <c r="C29" t="n">
-        <v>29.73609296095401</v>
+        <v>-4.705276496242732</v>
       </c>
       <c r="D29" t="n">
-        <v>-2653.409286273862</v>
+        <v>-2600.042040167002</v>
       </c>
       <c r="E29" t="n">
-        <v>-82.49248737723974</v>
+        <v>101.5507869919943</v>
       </c>
       <c r="F29" t="n">
-        <v>-52.75639441628573</v>
+        <v>96.84551049575157</v>
       </c>
     </row>
     <row r="30">
@@ -1027,19 +1027,19 @@
         <v>46027</v>
       </c>
       <c r="B30" t="n">
-        <v>2796.445072628424</v>
+        <v>2682.463532487159</v>
       </c>
       <c r="C30" t="n">
-        <v>50.18776911386976</v>
+        <v>32.11564441273003</v>
       </c>
       <c r="D30" t="n">
-        <v>-2666.914467843275</v>
+        <v>-2566.655311630478</v>
       </c>
       <c r="E30" t="n">
-        <v>-13.50518156941371</v>
+        <v>33.38672853652406</v>
       </c>
       <c r="F30" t="n">
-        <v>36.68258754445606</v>
+        <v>65.5023729492541</v>
       </c>
     </row>
     <row r="31">
@@ -1047,19 +1047,19 @@
         <v>46028</v>
       </c>
       <c r="B31" t="n">
-        <v>2813.102539878346</v>
+        <v>2688.180823457698</v>
       </c>
       <c r="C31" t="n">
-        <v>16.65746724992187</v>
+        <v>5.717290970539125</v>
       </c>
       <c r="D31" t="n">
-        <v>-2545.108488210074</v>
+        <v>-2573.57989917135</v>
       </c>
       <c r="E31" t="n">
-        <v>121.8059796332009</v>
+        <v>-6.92458754087238</v>
       </c>
       <c r="F31" t="n">
-        <v>138.4634468831227</v>
+        <v>-1.207296570333256</v>
       </c>
     </row>
     <row r="32">
@@ -1067,19 +1067,19 @@
         <v>46029</v>
       </c>
       <c r="B32" t="n">
-        <v>2858.335919840265</v>
+        <v>2737.126657947354</v>
       </c>
       <c r="C32" t="n">
-        <v>45.23337996191867</v>
+        <v>48.94583448965523</v>
       </c>
       <c r="D32" t="n">
-        <v>-2714.983601049047</v>
+        <v>-2600.244865754392</v>
       </c>
       <c r="E32" t="n">
-        <v>-169.8751128389727</v>
+        <v>-26.66496658304231</v>
       </c>
       <c r="F32" t="n">
-        <v>-124.641732877054</v>
+        <v>22.28086790661291</v>
       </c>
     </row>
     <row r="33">
@@ -1087,19 +1087,19 @@
         <v>46030</v>
       </c>
       <c r="B33" t="n">
-        <v>2847.491454457608</v>
+        <v>2698.699056179212</v>
       </c>
       <c r="C33" t="n">
-        <v>-10.84446538265729</v>
+        <v>-38.42760176814136</v>
       </c>
       <c r="D33" t="n">
-        <v>-2674.493262650889</v>
+        <v>-2632.808443253935</v>
       </c>
       <c r="E33" t="n">
-        <v>40.4903383981582</v>
+        <v>-32.56357749954259</v>
       </c>
       <c r="F33" t="n">
-        <v>29.64587301550091</v>
+        <v>-70.99117926768395</v>
       </c>
     </row>
     <row r="34">
@@ -1107,19 +1107,19 @@
         <v>46031</v>
       </c>
       <c r="B34" t="n">
-        <v>2892.258299285999</v>
+        <v>2732.279570697778</v>
       </c>
       <c r="C34" t="n">
-        <v>44.76684482839164</v>
+        <v>33.58051451856591</v>
       </c>
       <c r="D34" t="n">
-        <v>-2693.191851309896</v>
+        <v>-2627.587552796938</v>
       </c>
       <c r="E34" t="n">
-        <v>-18.69858865900733</v>
+        <v>5.220890456996585</v>
       </c>
       <c r="F34" t="n">
-        <v>26.06825616938431</v>
+        <v>38.80140497556249</v>
       </c>
     </row>
     <row r="35">
@@ -1127,19 +1127,19 @@
         <v>46034</v>
       </c>
       <c r="B35" t="n">
-        <v>2885.44899087578</v>
+        <v>2718.103145287891</v>
       </c>
       <c r="C35" t="n">
-        <v>-6.809308410219273</v>
+        <v>-14.17642540988709</v>
       </c>
       <c r="D35" t="n">
-        <v>-2679.091125755091</v>
+        <v>-2632.083956853078</v>
       </c>
       <c r="E35" t="n">
-        <v>14.10072555480565</v>
+        <v>-4.496404056139909</v>
       </c>
       <c r="F35" t="n">
-        <v>7.291417144586376</v>
+        <v>-18.672829466027</v>
       </c>
     </row>
     <row r="36">
@@ -1147,19 +1147,19 @@
         <v>46035</v>
       </c>
       <c r="B36" t="n">
-        <v>2874.38230046122</v>
+        <v>2711.20402183907</v>
       </c>
       <c r="C36" t="n">
-        <v>-11.06669041456053</v>
+        <v>-6.899123448820774</v>
       </c>
       <c r="D36" t="n">
-        <v>-2702.448220650197</v>
+        <v>-2634.708164494516</v>
       </c>
       <c r="E36" t="n">
-        <v>-23.357094895106</v>
+        <v>-2.624207641437351</v>
       </c>
       <c r="F36" t="n">
-        <v>-34.42378530966653</v>
+        <v>-9.523331090258125</v>
       </c>
     </row>
     <row r="37">
@@ -1167,19 +1167,19 @@
         <v>46036</v>
       </c>
       <c r="B37" t="n">
-        <v>2834.299692933663</v>
+        <v>2668.7204106635</v>
       </c>
       <c r="C37" t="n">
-        <v>-40.08260752755677</v>
+        <v>-42.48361117557033</v>
       </c>
       <c r="D37" t="n">
-        <v>-2628.625083915956</v>
+        <v>-2626.773248374323</v>
       </c>
       <c r="E37" t="n">
-        <v>73.82313673424096</v>
+        <v>7.934916120193066</v>
       </c>
       <c r="F37" t="n">
-        <v>33.74052920668419</v>
+        <v>-34.54869505537727</v>
       </c>
     </row>
     <row r="38">
@@ -1187,19 +1187,19 @@
         <v>46037</v>
       </c>
       <c r="B38" t="n">
-        <v>2828.178823906053</v>
+        <v>2705.356246249571</v>
       </c>
       <c r="C38" t="n">
-        <v>-6.120869027609842</v>
+        <v>36.63583558607115</v>
       </c>
       <c r="D38" t="n">
-        <v>-2674.113110071467</v>
+        <v>-2614.031451715319</v>
       </c>
       <c r="E38" t="n">
-        <v>-45.48802615551131</v>
+        <v>12.74179665900328</v>
       </c>
       <c r="F38" t="n">
-        <v>-51.60889518312115</v>
+        <v>49.37763224507444</v>
       </c>
     </row>
     <row r="39">
@@ -1207,19 +1207,19 @@
         <v>46038</v>
       </c>
       <c r="B39" t="n">
-        <v>2826.285776308456</v>
+        <v>2706.777821748281</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.893047597596706</v>
+        <v>1.421575498709444</v>
       </c>
       <c r="D39" t="n">
-        <v>-2650.537801213116</v>
+        <v>-2635.287529139244</v>
       </c>
       <c r="E39" t="n">
-        <v>23.57530885835104</v>
+        <v>-21.25607742392503</v>
       </c>
       <c r="F39" t="n">
-        <v>21.68226126075433</v>
+        <v>-19.83450192521559</v>
       </c>
     </row>
     <row r="40">
@@ -1227,19 +1227,19 @@
         <v>46041</v>
       </c>
       <c r="B40" t="n">
-        <v>2768.810334996146</v>
+        <v>2651.520913707935</v>
       </c>
       <c r="C40" t="n">
-        <v>-57.47544131231052</v>
+        <v>-55.25690804034593</v>
       </c>
       <c r="D40" t="n">
-        <v>-2607.075729171989</v>
+        <v>-2654.245582789777</v>
       </c>
       <c r="E40" t="n">
-        <v>43.4620720411267</v>
+        <v>-18.95805365053229</v>
       </c>
       <c r="F40" t="n">
-        <v>-14.01336927118382</v>
+        <v>-74.21496169087823</v>
       </c>
     </row>
     <row r="41">
@@ -1247,19 +1247,19 @@
         <v>46042</v>
       </c>
       <c r="B41" t="n">
-        <v>2709.410218576823</v>
+        <v>2622.084186151447</v>
       </c>
       <c r="C41" t="n">
-        <v>-59.40011641932279</v>
+        <v>-29.43672755648777</v>
       </c>
       <c r="D41" t="n">
-        <v>-2596.033947161373</v>
+        <v>-2651.689484943357</v>
       </c>
       <c r="E41" t="n">
-        <v>11.04178201061586</v>
+        <v>2.556097846419107</v>
       </c>
       <c r="F41" t="n">
-        <v>-48.35833440870692</v>
+        <v>-26.88062971006866</v>
       </c>
     </row>
     <row r="42">
@@ -1267,19 +1267,19 @@
         <v>46043</v>
       </c>
       <c r="B42" t="n">
-        <v>2705.658298441234</v>
+        <v>2617.783989236915</v>
       </c>
       <c r="C42" t="n">
-        <v>-3.751920135588534</v>
+        <v>-4.300196914531625</v>
       </c>
       <c r="D42" t="n">
-        <v>-2605.609559748093</v>
+        <v>-2639.152756064332</v>
       </c>
       <c r="E42" t="n">
-        <v>-9.575612586719672</v>
+        <v>12.53672887902576</v>
       </c>
       <c r="F42" t="n">
-        <v>-13.32753272230821</v>
+        <v>8.236531964494134</v>
       </c>
     </row>
     <row r="43">
@@ -1287,19 +1287,19 @@
         <v>46044</v>
       </c>
       <c r="B43" t="n">
-        <v>2729.343768401946</v>
+        <v>2651.217242249824</v>
       </c>
       <c r="C43" t="n">
-        <v>23.68546996071154</v>
+        <v>33.43325301290906</v>
       </c>
       <c r="D43" t="n">
-        <v>-2694.293932487305</v>
+        <v>-2656.810612194547</v>
       </c>
       <c r="E43" t="n">
-        <v>-88.68437273921199</v>
+        <v>-17.65785613021535</v>
       </c>
       <c r="F43" t="n">
-        <v>-64.99890277850045</v>
+        <v>15.77539688269371</v>
       </c>
     </row>
     <row r="44">
@@ -1307,19 +1307,19 @@
         <v>46045</v>
       </c>
       <c r="B44" t="n">
-        <v>2731.962868869332</v>
+        <v>2650.300562427095</v>
       </c>
       <c r="C44" t="n">
-        <v>2.619100467386033</v>
+        <v>-0.9166798227288382</v>
       </c>
       <c r="D44" t="n">
-        <v>-2680.96890347209</v>
+        <v>-2678.895366678237</v>
       </c>
       <c r="E44" t="n">
-        <v>13.32502901521457</v>
+        <v>-22.08475448369018</v>
       </c>
       <c r="F44" t="n">
-        <v>15.9441294826006</v>
+        <v>-23.00143430641901</v>
       </c>
     </row>
     <row r="45">
@@ -1327,19 +1327,19 @@
         <v>46048</v>
       </c>
       <c r="B45" t="n">
-        <v>2707.45927665296</v>
+        <v>2625.594513440042</v>
       </c>
       <c r="C45" t="n">
-        <v>-24.503592216372</v>
+        <v>-24.70604898705369</v>
       </c>
       <c r="D45" t="n">
-        <v>-2672.051683498611</v>
+        <v>-2694.3764844589</v>
       </c>
       <c r="E45" t="n">
-        <v>8.91721997347986</v>
+        <v>-15.48111778066232</v>
       </c>
       <c r="F45" t="n">
-        <v>-15.58637224289214</v>
+        <v>-40.18716676771601</v>
       </c>
     </row>
     <row r="46">
@@ -1347,19 +1347,19 @@
         <v>46049</v>
       </c>
       <c r="B46" t="n">
-        <v>2714.822213335793</v>
+        <v>2627.989232911538</v>
       </c>
       <c r="C46" t="n">
-        <v>7.362936682832697</v>
+        <v>2.394719471496046</v>
       </c>
       <c r="D46" t="n">
-        <v>-2666.234127977557</v>
+        <v>-2686.122191894891</v>
       </c>
       <c r="E46" t="n">
-        <v>5.817555521053237</v>
+        <v>8.254292564008665</v>
       </c>
       <c r="F46" t="n">
-        <v>13.18049220388593</v>
+        <v>10.64901203550471</v>
       </c>
     </row>
     <row r="47">
@@ -1367,19 +1367,19 @@
         <v>46050</v>
       </c>
       <c r="B47" t="n">
-        <v>2717.94962428243</v>
+        <v>2634.196034396073</v>
       </c>
       <c r="C47" t="n">
-        <v>3.127410946637156</v>
+        <v>6.20680148453539</v>
       </c>
       <c r="D47" t="n">
-        <v>-2651.802771761997</v>
+        <v>-2682.122519572552</v>
       </c>
       <c r="E47" t="n">
-        <v>14.43135621556075</v>
+        <v>3.999672322338938</v>
       </c>
       <c r="F47" t="n">
-        <v>17.55876716219791</v>
+        <v>10.20647380687433</v>
       </c>
     </row>
     <row r="48">
@@ -1387,19 +1387,19 @@
         <v>46051</v>
       </c>
       <c r="B48" t="n">
-        <v>2709.649426137021</v>
+        <v>2619.097986739941</v>
       </c>
       <c r="C48" t="n">
-        <v>-8.300198145408558</v>
+        <v>-15.09804765613217</v>
       </c>
       <c r="D48" t="n">
-        <v>-2613.434677459428</v>
+        <v>-2693.469318282374</v>
       </c>
       <c r="E48" t="n">
-        <v>38.36809430256835</v>
+        <v>-11.34679870982245</v>
       </c>
       <c r="F48" t="n">
-        <v>30.06789615715979</v>
+        <v>-26.44484636595462</v>
       </c>
     </row>
     <row r="49">
@@ -1407,19 +1407,19 @@
         <v>46052</v>
       </c>
       <c r="B49" t="n">
-        <v>2651.906532926916</v>
+        <v>2602.981011882974</v>
       </c>
       <c r="C49" t="n">
-        <v>-57.74289321010474</v>
+        <v>-16.11697485696732</v>
       </c>
       <c r="D49" t="n">
-        <v>-2621.500000547868</v>
+        <v>-2691.7140071507</v>
       </c>
       <c r="E49" t="n">
-        <v>-8.065323088439982</v>
+        <v>1.755311131674262</v>
       </c>
       <c r="F49" t="n">
-        <v>-65.80821629854472</v>
+        <v>-14.36166372529306</v>
       </c>
     </row>
   </sheetData>
@@ -1487,19 +1487,19 @@
         <v>45985</v>
       </c>
       <c r="B3" t="n">
-        <v>2546.703045659474</v>
+        <v>2518.505478472742</v>
       </c>
       <c r="C3" t="n">
-        <v>46.7030456594739</v>
+        <v>18.50547847274174</v>
       </c>
       <c r="D3" t="n">
-        <v>-2502.522774194714</v>
+        <v>-2518.905173580478</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.522774194714657</v>
+        <v>-18.90517358047873</v>
       </c>
       <c r="F3" t="n">
-        <v>44.18027146475924</v>
+        <v>-0.3996951077369886</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         <v>45986</v>
       </c>
       <c r="B4" t="n">
-        <v>2561.425246197936</v>
+        <v>2552.59661447856</v>
       </c>
       <c r="C4" t="n">
-        <v>14.72220053846195</v>
+        <v>34.0911360058185</v>
       </c>
       <c r="D4" t="n">
-        <v>-2542.923669761187</v>
+        <v>-2549.397919023105</v>
       </c>
       <c r="E4" t="n">
-        <v>-40.40089556647263</v>
+        <v>-30.49274544262653</v>
       </c>
       <c r="F4" t="n">
-        <v>-25.67869502801068</v>
+        <v>3.59839056319197</v>
       </c>
     </row>
     <row r="5">
@@ -1527,19 +1527,19 @@
         <v>45987</v>
       </c>
       <c r="B5" t="n">
-        <v>2599.908135257944</v>
+        <v>2581.602479781228</v>
       </c>
       <c r="C5" t="n">
-        <v>38.48288906000835</v>
+        <v>29.00586530266764</v>
       </c>
       <c r="D5" t="n">
-        <v>-2559.75244503935</v>
+        <v>-2563.973628990111</v>
       </c>
       <c r="E5" t="n">
-        <v>-16.82877527816299</v>
+        <v>-14.57570996700633</v>
       </c>
       <c r="F5" t="n">
-        <v>21.65411378184535</v>
+        <v>14.43015533566131</v>
       </c>
     </row>
     <row r="6">
@@ -1547,19 +1547,19 @@
         <v>45989</v>
       </c>
       <c r="B6" t="n">
-        <v>2624.788635991301</v>
+        <v>2595.861780852896</v>
       </c>
       <c r="C6" t="n">
-        <v>24.88050073335717</v>
+        <v>14.25930107166778</v>
       </c>
       <c r="D6" t="n">
-        <v>-2567.963117268093</v>
+        <v>-2582.600097418465</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.210672228743078</v>
+        <v>-18.6264684283542</v>
       </c>
       <c r="F6" t="n">
-        <v>16.66982850461409</v>
+        <v>-4.367167356686423</v>
       </c>
     </row>
     <row r="7">
@@ -1567,19 +1567,19 @@
         <v>45992</v>
       </c>
       <c r="B7" t="n">
-        <v>2619.617435095059</v>
+        <v>2590.23315347662</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.171200896242226</v>
+        <v>-5.62862737627529</v>
       </c>
       <c r="D7" t="n">
-        <v>-2565.024349678032</v>
+        <v>-2567.850552598236</v>
       </c>
       <c r="E7" t="n">
-        <v>2.938767590060706</v>
+        <v>14.7495448202294</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.23243330618152</v>
+        <v>9.120917443954113</v>
       </c>
     </row>
     <row r="8">
@@ -1587,19 +1587,19 @@
         <v>45993</v>
       </c>
       <c r="B8" t="n">
-        <v>2657.979839568095</v>
+        <v>2600.478818342249</v>
       </c>
       <c r="C8" t="n">
-        <v>38.36240447303589</v>
+        <v>10.24566486562844</v>
       </c>
       <c r="D8" t="n">
-        <v>-2552.41550780506</v>
+        <v>-2571.11397114153</v>
       </c>
       <c r="E8" t="n">
-        <v>12.60884187297233</v>
+        <v>-3.263418543293938</v>
       </c>
       <c r="F8" t="n">
-        <v>50.97124634600823</v>
+        <v>6.982246322334504</v>
       </c>
     </row>
     <row r="9">
@@ -1607,19 +1607,19 @@
         <v>45994</v>
       </c>
       <c r="B9" t="n">
-        <v>2696.855787346133</v>
+        <v>2645.983844916559</v>
       </c>
       <c r="C9" t="n">
-        <v>38.8759477780377</v>
+        <v>45.5050265743098</v>
       </c>
       <c r="D9" t="n">
-        <v>-2593.340324175035</v>
+        <v>-2613.560836623747</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.92481636997491</v>
+        <v>-42.44686548221762</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.048868591937207</v>
+        <v>3.058161092092178</v>
       </c>
     </row>
     <row r="10">
@@ -1627,19 +1627,19 @@
         <v>45995</v>
       </c>
       <c r="B10" t="n">
-        <v>2732.411225654889</v>
+        <v>2665.127221534397</v>
       </c>
       <c r="C10" t="n">
-        <v>35.55543830875604</v>
+        <v>19.14337661783793</v>
       </c>
       <c r="D10" t="n">
-        <v>-2601.429708552707</v>
+        <v>-2607.428328886966</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.089384377672559</v>
+        <v>6.132507736781463</v>
       </c>
       <c r="F10" t="n">
-        <v>27.46605393108348</v>
+        <v>25.27588435461939</v>
       </c>
     </row>
     <row r="11">
@@ -1647,19 +1647,19 @@
         <v>45996</v>
       </c>
       <c r="B11" t="n">
-        <v>2755.782258284519</v>
+        <v>2672.742079173148</v>
       </c>
       <c r="C11" t="n">
-        <v>23.37103262963001</v>
+        <v>7.614857638751801</v>
       </c>
       <c r="D11" t="n">
-        <v>-2606.279638262674</v>
+        <v>-2630.01923707589</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.849929709966545</v>
+        <v>-22.59090818892446</v>
       </c>
       <c r="F11" t="n">
-        <v>18.52110291966346</v>
+        <v>-14.97605055017266</v>
       </c>
     </row>
     <row r="12">
@@ -1667,19 +1667,19 @@
         <v>45999</v>
       </c>
       <c r="B12" t="n">
-        <v>2723.410717127338</v>
+        <v>2652.885296537138</v>
       </c>
       <c r="C12" t="n">
-        <v>-32.37154115718113</v>
+        <v>-19.85678263600994</v>
       </c>
       <c r="D12" t="n">
-        <v>-2582.284361149211</v>
+        <v>-2612.183350221286</v>
       </c>
       <c r="E12" t="n">
-        <v>23.99527711346263</v>
+        <v>17.83588685460472</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.376264043718493</v>
+        <v>-2.020895781405216</v>
       </c>
     </row>
     <row r="13">
@@ -1687,19 +1687,19 @@
         <v>46000</v>
       </c>
       <c r="B13" t="n">
-        <v>2724.325335064285</v>
+        <v>2646.50979390019</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9146179369477068</v>
+        <v>-6.375502636948568</v>
       </c>
       <c r="D13" t="n">
-        <v>-2581.371833129074</v>
+        <v>-2611.94094298619</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9125280201369605</v>
+        <v>0.2424072350954702</v>
       </c>
       <c r="F13" t="n">
-        <v>1.827145957084667</v>
+        <v>-6.133095401853097</v>
       </c>
     </row>
     <row r="14">
@@ -1707,19 +1707,19 @@
         <v>46001</v>
       </c>
       <c r="B14" t="n">
-        <v>2780.337650930097</v>
+        <v>2694.921749504646</v>
       </c>
       <c r="C14" t="n">
-        <v>56.01231586581116</v>
+        <v>48.41195560445613</v>
       </c>
       <c r="D14" t="n">
-        <v>-2631.904814623981</v>
+        <v>-2665.38451790161</v>
       </c>
       <c r="E14" t="n">
-        <v>-50.53298149490638</v>
+        <v>-53.44357491541996</v>
       </c>
       <c r="F14" t="n">
-        <v>5.47933437090478</v>
+        <v>-5.031619310963833</v>
       </c>
     </row>
     <row r="15">
@@ -1727,19 +1727,19 @@
         <v>46002</v>
       </c>
       <c r="B15" t="n">
-        <v>2791.638137881665</v>
+        <v>2722.710357192101</v>
       </c>
       <c r="C15" t="n">
-        <v>11.30048695156847</v>
+        <v>27.78860768745471</v>
       </c>
       <c r="D15" t="n">
-        <v>-2671.582843338219</v>
+        <v>-2702.800744980435</v>
       </c>
       <c r="E15" t="n">
-        <v>-39.67802871423828</v>
+        <v>-37.4162270788247</v>
       </c>
       <c r="F15" t="n">
-        <v>-28.37754176266981</v>
+        <v>-9.62761939136999</v>
       </c>
     </row>
     <row r="16">
@@ -1747,19 +1747,19 @@
         <v>46003</v>
       </c>
       <c r="B16" t="n">
-        <v>2799.488550776931</v>
+        <v>2706.008880270886</v>
       </c>
       <c r="C16" t="n">
-        <v>7.850412895266345</v>
+        <v>-16.70147692121418</v>
       </c>
       <c r="D16" t="n">
-        <v>-2662.765885052453</v>
+        <v>-2690.447912448921</v>
       </c>
       <c r="E16" t="n">
-        <v>8.81695828576585</v>
+        <v>12.3528325315142</v>
       </c>
       <c r="F16" t="n">
-        <v>16.66737118103219</v>
+        <v>-4.348644389699984</v>
       </c>
     </row>
     <row r="17">
@@ -1767,19 +1767,19 @@
         <v>46006</v>
       </c>
       <c r="B17" t="n">
-        <v>2777.833815980128</v>
+        <v>2703.487200371317</v>
       </c>
       <c r="C17" t="n">
-        <v>-21.6547347968035</v>
+        <v>-2.52167989956979</v>
       </c>
       <c r="D17" t="n">
-        <v>-2682.881611689438</v>
+        <v>-2704.710495215662</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.11572663698462</v>
+        <v>-14.26258276674162</v>
       </c>
       <c r="F17" t="n">
-        <v>-41.77046143378811</v>
+        <v>-16.78426266631141</v>
       </c>
     </row>
     <row r="18">
@@ -1787,19 +1787,19 @@
         <v>46007</v>
       </c>
       <c r="B18" t="n">
-        <v>2793.179111708708</v>
+        <v>2691.18003707549</v>
       </c>
       <c r="C18" t="n">
-        <v>15.34529572858037</v>
+        <v>-12.30716329582719</v>
       </c>
       <c r="D18" t="n">
-        <v>-2656.430470050338</v>
+        <v>-2679.264940547659</v>
       </c>
       <c r="E18" t="n">
-        <v>26.45114163909966</v>
+        <v>25.4455546680033</v>
       </c>
       <c r="F18" t="n">
-        <v>41.79643736768003</v>
+        <v>13.1383913721761</v>
       </c>
     </row>
     <row r="19">
@@ -1807,19 +1807,19 @@
         <v>46008</v>
       </c>
       <c r="B19" t="n">
-        <v>2787.224152925993</v>
+        <v>2688.241475025948</v>
       </c>
       <c r="C19" t="n">
-        <v>-5.954958782715039</v>
+        <v>-2.93856204954136</v>
       </c>
       <c r="D19" t="n">
-        <v>-2671.299374636032</v>
+        <v>-2690.740977824901</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.86890458569405</v>
+        <v>-11.47603727724163</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.82386336840909</v>
+        <v>-14.41459932678299</v>
       </c>
     </row>
     <row r="20">
@@ -1827,19 +1827,19 @@
         <v>46009</v>
       </c>
       <c r="B20" t="n">
-        <v>2835.666810168239</v>
+        <v>2714.801780026838</v>
       </c>
       <c r="C20" t="n">
-        <v>48.44265724224624</v>
+        <v>26.56030500088946</v>
       </c>
       <c r="D20" t="n">
-        <v>-2654.329738517083</v>
+        <v>-2690.976509993996</v>
       </c>
       <c r="E20" t="n">
-        <v>16.96963611894898</v>
+        <v>-0.2355321690956771</v>
       </c>
       <c r="F20" t="n">
-        <v>65.41229336119522</v>
+        <v>26.32477283179378</v>
       </c>
     </row>
     <row r="21">
@@ -1847,19 +1847,19 @@
         <v>46010</v>
       </c>
       <c r="B21" t="n">
-        <v>2842.30818006141</v>
+        <v>2724.320592864507</v>
       </c>
       <c r="C21" t="n">
-        <v>6.641369893170122</v>
+        <v>9.518812837669429</v>
       </c>
       <c r="D21" t="n">
-        <v>-2653.994496116591</v>
+        <v>-2718.880945080117</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3352424004920067</v>
+        <v>-27.90443508612043</v>
       </c>
       <c r="F21" t="n">
-        <v>6.976612293662129</v>
+        <v>-18.385622248451</v>
       </c>
     </row>
     <row r="22">
@@ -1867,19 +1867,19 @@
         <v>46013</v>
       </c>
       <c r="B22" t="n">
-        <v>2887.216508430169</v>
+        <v>2755.417158355735</v>
       </c>
       <c r="C22" t="n">
-        <v>44.90832836875961</v>
+        <v>31.09656549122792</v>
       </c>
       <c r="D22" t="n">
-        <v>-2688.470180254278</v>
+        <v>-2746.718093207429</v>
       </c>
       <c r="E22" t="n">
-        <v>-34.47568413768704</v>
+        <v>-27.8371481273125</v>
       </c>
       <c r="F22" t="n">
-        <v>10.43264423107257</v>
+        <v>3.259417363915418</v>
       </c>
     </row>
     <row r="23">
@@ -1887,19 +1887,19 @@
         <v>46014</v>
       </c>
       <c r="B23" t="n">
-        <v>2873.547980840213</v>
+        <v>2742.244300776659</v>
       </c>
       <c r="C23" t="n">
-        <v>-13.66852758995583</v>
+        <v>-13.17285757907575</v>
       </c>
       <c r="D23" t="n">
-        <v>-2682.508835119927</v>
+        <v>-2724.865048156164</v>
       </c>
       <c r="E23" t="n">
-        <v>5.961345134350722</v>
+        <v>21.85304505126533</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.707182455605107</v>
+        <v>8.680187472189573</v>
       </c>
     </row>
     <row r="24">
@@ -1907,19 +1907,19 @@
         <v>46015</v>
       </c>
       <c r="B24" t="n">
-        <v>2870.974175837074</v>
+        <v>2744.503732995572</v>
       </c>
       <c r="C24" t="n">
-        <v>-2.573805003139114</v>
+        <v>2.25943221891248</v>
       </c>
       <c r="D24" t="n">
-        <v>-2683.879854602138</v>
+        <v>-2733.808792217947</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.371019482210613</v>
+        <v>-8.943744061783491</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.944824485349727</v>
+        <v>-6.684311842871011</v>
       </c>
     </row>
     <row r="25">
@@ -1927,19 +1927,19 @@
         <v>46017</v>
       </c>
       <c r="B25" t="n">
-        <v>2857.341291776481</v>
+        <v>2742.432026886738</v>
       </c>
       <c r="C25" t="n">
-        <v>-13.63288406059291</v>
+        <v>-2.071706108833951</v>
       </c>
       <c r="D25" t="n">
-        <v>-2686.567913381256</v>
+        <v>-2721.875335880784</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.688058779118364</v>
+        <v>11.93345633716308</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.32094283971128</v>
+        <v>9.861750228329129</v>
       </c>
     </row>
     <row r="26">
@@ -1947,19 +1947,19 @@
         <v>46020</v>
       </c>
       <c r="B26" t="n">
-        <v>2859.202334123705</v>
+        <v>2743.371772152091</v>
       </c>
       <c r="C26" t="n">
-        <v>1.861042347224156</v>
+        <v>0.9397452653529399</v>
       </c>
       <c r="D26" t="n">
-        <v>-2683.606081666027</v>
+        <v>-2708.573115538455</v>
       </c>
       <c r="E26" t="n">
-        <v>2.961831715229891</v>
+        <v>13.30222034232929</v>
       </c>
       <c r="F26" t="n">
-        <v>4.822874062454048</v>
+        <v>14.24196560768223</v>
       </c>
     </row>
     <row r="27">
@@ -1967,19 +1967,19 @@
         <v>46021</v>
       </c>
       <c r="B27" t="n">
-        <v>2839.94991297464</v>
+        <v>2738.280240351294</v>
       </c>
       <c r="C27" t="n">
-        <v>-19.25242114906587</v>
+        <v>-5.091531800796474</v>
       </c>
       <c r="D27" t="n">
-        <v>-2692.748039469854</v>
+        <v>-2700.647046548419</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.141957803827609</v>
+        <v>7.926068990036583</v>
       </c>
       <c r="F27" t="n">
-        <v>-28.39437895289348</v>
+        <v>2.834537189240109</v>
       </c>
     </row>
     <row r="28">
@@ -1987,19 +1987,19 @@
         <v>46022</v>
       </c>
       <c r="B28" t="n">
-        <v>2805.174322897041</v>
+        <v>2714.944532621374</v>
       </c>
       <c r="C28" t="n">
-        <v>-34.77559007759874</v>
+        <v>-23.33570772992061</v>
       </c>
       <c r="D28" t="n">
-        <v>-2668.389154493989</v>
+        <v>-2673.980123672371</v>
       </c>
       <c r="E28" t="n">
-        <v>24.35888497586484</v>
+        <v>26.66692287604792</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.4167051017339</v>
+        <v>3.331215146127306</v>
       </c>
     </row>
     <row r="29">
@@ -2007,19 +2007,19 @@
         <v>46024</v>
       </c>
       <c r="B29" t="n">
-        <v>2826.988563693496</v>
+        <v>2729.45233609234</v>
       </c>
       <c r="C29" t="n">
-        <v>21.81424079645512</v>
+        <v>14.50780347096634</v>
       </c>
       <c r="D29" t="n">
-        <v>-2704.1540603873</v>
+        <v>-2698.965345226561</v>
       </c>
       <c r="E29" t="n">
-        <v>-35.76490589331115</v>
+        <v>-24.98522155419005</v>
       </c>
       <c r="F29" t="n">
-        <v>-13.95066509685603</v>
+        <v>-10.47741808322371</v>
       </c>
     </row>
     <row r="30">
@@ -2027,19 +2027,19 @@
         <v>46027</v>
       </c>
       <c r="B30" t="n">
-        <v>2862.85640648413</v>
+        <v>2761.978058810208</v>
       </c>
       <c r="C30" t="n">
-        <v>35.86784279063386</v>
+        <v>32.52572271786858</v>
       </c>
       <c r="D30" t="n">
-        <v>-2724.523319712252</v>
+        <v>-2717.104205594345</v>
       </c>
       <c r="E30" t="n">
-        <v>-20.36925932495114</v>
+        <v>-18.13886036778467</v>
       </c>
       <c r="F30" t="n">
-        <v>15.49858346568271</v>
+        <v>14.3868623500839</v>
       </c>
     </row>
     <row r="31">
@@ -2047,19 +2047,19 @@
         <v>46028</v>
       </c>
       <c r="B31" t="n">
-        <v>2899.437276342252</v>
+        <v>2791.377421850616</v>
       </c>
       <c r="C31" t="n">
-        <v>36.58086985812179</v>
+        <v>29.39936304040702</v>
       </c>
       <c r="D31" t="n">
-        <v>-2733.361877284245</v>
+        <v>-2778.62318898213</v>
       </c>
       <c r="E31" t="n">
-        <v>-8.838557571993078</v>
+        <v>-61.51898338778483</v>
       </c>
       <c r="F31" t="n">
-        <v>27.74231228612871</v>
+        <v>-32.1196203473778</v>
       </c>
     </row>
     <row r="32">
@@ -2067,19 +2067,19 @@
         <v>46029</v>
       </c>
       <c r="B32" t="n">
-        <v>2852.13160031205</v>
+        <v>2743.372716177041</v>
       </c>
       <c r="C32" t="n">
-        <v>-47.30567603020154</v>
+        <v>-48.00470567357479</v>
       </c>
       <c r="D32" t="n">
-        <v>-2692.761868282458</v>
+        <v>-2743.030528268543</v>
       </c>
       <c r="E32" t="n">
-        <v>40.60000900178693</v>
+        <v>35.59266071358707</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.705667028414609</v>
+        <v>-12.41204495998772</v>
       </c>
     </row>
     <row r="33">
@@ -2087,19 +2087,19 @@
         <v>46030</v>
       </c>
       <c r="B33" t="n">
-        <v>2889.805703842791</v>
+        <v>2803.053363582947</v>
       </c>
       <c r="C33" t="n">
-        <v>37.67410353074047</v>
+        <v>59.68064740590671</v>
       </c>
       <c r="D33" t="n">
-        <v>-2759.149137068953</v>
+        <v>-2760.483389582276</v>
       </c>
       <c r="E33" t="n">
-        <v>-66.38726878649504</v>
+        <v>-17.45286131373314</v>
       </c>
       <c r="F33" t="n">
-        <v>-28.71316525575457</v>
+        <v>42.22778609217357</v>
       </c>
     </row>
     <row r="34">
@@ -2107,19 +2107,19 @@
         <v>46031</v>
       </c>
       <c r="B34" t="n">
-        <v>2890.23556251645</v>
+        <v>2822.102896890554</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4298586736590551</v>
+        <v>19.04953330760645</v>
       </c>
       <c r="D34" t="n">
-        <v>-2732.518847563194</v>
+        <v>-2768.664902807069</v>
       </c>
       <c r="E34" t="n">
-        <v>26.63028950575881</v>
+        <v>-8.181513224792525</v>
       </c>
       <c r="F34" t="n">
-        <v>27.06014817941787</v>
+        <v>10.86802008281393</v>
       </c>
     </row>
     <row r="35">
@@ -2127,19 +2127,19 @@
         <v>46034</v>
       </c>
       <c r="B35" t="n">
-        <v>2948.67879492302</v>
+        <v>2834.799908839699</v>
       </c>
       <c r="C35" t="n">
-        <v>58.44323240657013</v>
+        <v>12.69701194914478</v>
       </c>
       <c r="D35" t="n">
-        <v>-2682.53311421062</v>
+        <v>-2761.299248794939</v>
       </c>
       <c r="E35" t="n">
-        <v>49.98573335257379</v>
+        <v>7.365654012130108</v>
       </c>
       <c r="F35" t="n">
-        <v>108.4289657591439</v>
+        <v>20.06266596127489</v>
       </c>
     </row>
     <row r="36">
@@ -2147,19 +2147,19 @@
         <v>46035</v>
       </c>
       <c r="B36" t="n">
-        <v>2972.866885317502</v>
+        <v>2839.039785090927</v>
       </c>
       <c r="C36" t="n">
-        <v>24.18809039448251</v>
+        <v>4.239876251227997</v>
       </c>
       <c r="D36" t="n">
-        <v>-2670.295329095148</v>
+        <v>-2797.777550030299</v>
       </c>
       <c r="E36" t="n">
-        <v>12.23778511547198</v>
+        <v>-36.47830123536005</v>
       </c>
       <c r="F36" t="n">
-        <v>36.42587550995449</v>
+        <v>-32.23842498413205</v>
       </c>
     </row>
     <row r="37">
@@ -2167,19 +2167,19 @@
         <v>46036</v>
       </c>
       <c r="B37" t="n">
-        <v>2943.703496003448</v>
+        <v>2850.115413751273</v>
       </c>
       <c r="C37" t="n">
-        <v>-29.16338931405471</v>
+        <v>11.07562866034596</v>
       </c>
       <c r="D37" t="n">
-        <v>-2670.422932894412</v>
+        <v>-2819.365226930061</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.1276037992638521</v>
+        <v>-21.58767689976185</v>
       </c>
       <c r="F37" t="n">
-        <v>-29.29099311331856</v>
+        <v>-10.51204823941589</v>
       </c>
     </row>
     <row r="38">
@@ -2187,19 +2187,19 @@
         <v>46037</v>
       </c>
       <c r="B38" t="n">
-        <v>2951.502064745854</v>
+        <v>2865.40216097014</v>
       </c>
       <c r="C38" t="n">
-        <v>7.798568742406133</v>
+        <v>15.28674721886773</v>
       </c>
       <c r="D38" t="n">
-        <v>-2667.815869926057</v>
+        <v>-2816.639098792446</v>
       </c>
       <c r="E38" t="n">
-        <v>2.607062968355422</v>
+        <v>2.726128137614978</v>
       </c>
       <c r="F38" t="n">
-        <v>10.40563171076155</v>
+        <v>18.01287535648271</v>
       </c>
     </row>
     <row r="39">
@@ -2207,19 +2207,19 @@
         <v>46038</v>
       </c>
       <c r="B39" t="n">
-        <v>2953.174407102439</v>
+        <v>2858.698588918869</v>
       </c>
       <c r="C39" t="n">
-        <v>1.672342356585432</v>
+        <v>-6.703572051271294</v>
       </c>
       <c r="D39" t="n">
-        <v>-2658.856208522833</v>
+        <v>-2814.975586417066</v>
       </c>
       <c r="E39" t="n">
-        <v>8.959661403223436</v>
+        <v>1.663512375379469</v>
       </c>
       <c r="F39" t="n">
-        <v>10.63200375980887</v>
+        <v>-5.040059675891825</v>
       </c>
     </row>
     <row r="40">
@@ -2227,19 +2227,19 @@
         <v>46042</v>
       </c>
       <c r="B40" t="n">
-        <v>2891.482072107942</v>
+        <v>2805.222333399543</v>
       </c>
       <c r="C40" t="n">
-        <v>-61.69233499449729</v>
+        <v>-53.47625551932651</v>
       </c>
       <c r="D40" t="n">
-        <v>-2604.775848935642</v>
+        <v>-2779.039731104067</v>
       </c>
       <c r="E40" t="n">
-        <v>54.0803595871912</v>
+        <v>35.93585531299868</v>
       </c>
       <c r="F40" t="n">
-        <v>-7.61197540730609</v>
+        <v>-17.54040020632783</v>
       </c>
     </row>
     <row r="41">
@@ -2247,19 +2247,19 @@
         <v>46043</v>
       </c>
       <c r="B41" t="n">
-        <v>2935.564011480621</v>
+        <v>2853.263356982495</v>
       </c>
       <c r="C41" t="n">
-        <v>44.08193937267924</v>
+        <v>48.04102358295268</v>
       </c>
       <c r="D41" t="n">
-        <v>-2652.684043575804</v>
+        <v>-2845.569188048556</v>
       </c>
       <c r="E41" t="n">
-        <v>-47.90819464016158</v>
+        <v>-66.52945694448908</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.826255267482338</v>
+        <v>-18.48843336153641</v>
       </c>
     </row>
     <row r="42">
@@ -2267,19 +2267,19 @@
         <v>46044</v>
       </c>
       <c r="B42" t="n">
-        <v>2973.526708542764</v>
+        <v>2869.402477864648</v>
       </c>
       <c r="C42" t="n">
-        <v>37.96269706214252</v>
+        <v>16.13912088215238</v>
       </c>
       <c r="D42" t="n">
-        <v>-2668.565279445063</v>
+        <v>-2856.485032058857</v>
       </c>
       <c r="E42" t="n">
-        <v>-15.88123586925894</v>
+        <v>-10.91584401030059</v>
       </c>
       <c r="F42" t="n">
-        <v>22.08146119288358</v>
+        <v>5.223276871851795</v>
       </c>
     </row>
     <row r="43">
@@ -2287,19 +2287,19 @@
         <v>46045</v>
       </c>
       <c r="B43" t="n">
-        <v>2932.066484524338</v>
+        <v>2850.701084169656</v>
       </c>
       <c r="C43" t="n">
-        <v>-41.46022401842538</v>
+        <v>-18.70139369499111</v>
       </c>
       <c r="D43" t="n">
-        <v>-2665.675610882332</v>
+        <v>-2838.80198301088</v>
       </c>
       <c r="E43" t="n">
-        <v>2.889668562731003</v>
+        <v>17.68304904797697</v>
       </c>
       <c r="F43" t="n">
-        <v>-38.57055545569438</v>
+        <v>-1.018344647014146</v>
       </c>
     </row>
     <row r="44">
@@ -2307,19 +2307,19 @@
         <v>46048</v>
       </c>
       <c r="B44" t="n">
-        <v>2930.995152146335</v>
+        <v>2847.861174382941</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.071332378003262</v>
+        <v>-2.839909786715907</v>
       </c>
       <c r="D44" t="n">
-        <v>-2679.520508435027</v>
+        <v>-2841.487841434879</v>
       </c>
       <c r="E44" t="n">
-        <v>-13.84489755269578</v>
+        <v>-2.68585842399898</v>
       </c>
       <c r="F44" t="n">
-        <v>-14.91622993069905</v>
+        <v>-5.525768210714887</v>
       </c>
     </row>
     <row r="45">
@@ -2327,19 +2327,19 @@
         <v>46049</v>
       </c>
       <c r="B45" t="n">
-        <v>2923.15122592835</v>
+        <v>2831.921259646289</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.843926217984972</v>
+        <v>-15.93991473665164</v>
       </c>
       <c r="D45" t="n">
-        <v>-2670.911783173506</v>
+        <v>-2840.337227109911</v>
       </c>
       <c r="E45" t="n">
-        <v>8.608725261521158</v>
+        <v>1.150614324968046</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7647990435361862</v>
+        <v>-14.7893004116836</v>
       </c>
     </row>
     <row r="46">
@@ -2347,19 +2347,19 @@
         <v>46050</v>
       </c>
       <c r="B46" t="n">
-        <v>2897.342588132467</v>
+        <v>2818.766696390578</v>
       </c>
       <c r="C46" t="n">
-        <v>-25.80863779588344</v>
+        <v>-13.15456325571085</v>
       </c>
       <c r="D46" t="n">
-        <v>-2653.266992719067</v>
+        <v>-2843.372659262851</v>
       </c>
       <c r="E46" t="n">
-        <v>17.64479045443886</v>
+        <v>-3.035432152939848</v>
       </c>
       <c r="F46" t="n">
-        <v>-8.16384734144458</v>
+        <v>-16.1899954086507</v>
       </c>
     </row>
     <row r="47">
@@ -2367,19 +2367,19 @@
         <v>46051</v>
       </c>
       <c r="B47" t="n">
-        <v>2891.538853702082</v>
+        <v>2820.138567096584</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.803734430384793</v>
+        <v>1.371870706006121</v>
       </c>
       <c r="D47" t="n">
-        <v>-2683.389669371879</v>
+        <v>-2866.838186384458</v>
       </c>
       <c r="E47" t="n">
-        <v>-30.12267665281161</v>
+        <v>-23.46552712160701</v>
       </c>
       <c r="F47" t="n">
-        <v>-35.9264110831964</v>
+        <v>-22.09365641560089</v>
       </c>
     </row>
     <row r="48">
@@ -2387,19 +2387,19 @@
         <v>46052</v>
       </c>
       <c r="B48" t="n">
-        <v>2849.390310120856</v>
+        <v>2804.438614945791</v>
       </c>
       <c r="C48" t="n">
-        <v>-42.14854358122602</v>
+        <v>-15.69995215079325</v>
       </c>
       <c r="D48" t="n">
-        <v>-2746.792396730797</v>
+        <v>-2823.795643294407</v>
       </c>
       <c r="E48" t="n">
-        <v>-63.40272735891813</v>
+        <v>43.04254309005137</v>
       </c>
       <c r="F48" t="n">
-        <v>-105.5512709401441</v>
+        <v>27.34259093925812</v>
       </c>
     </row>
   </sheetData>
@@ -2457,16 +2457,16 @@
         <v>45985</v>
       </c>
       <c r="B3" t="n">
-        <v>-31.48491743213708</v>
+        <v>1.724962920131475</v>
       </c>
       <c r="C3" t="n">
-        <v>44.18027146475924</v>
+        <v>-0.3996951077369886</v>
       </c>
       <c r="D3" t="n">
-        <v>38.35093009093685</v>
+        <v>-0.3469575587994693</v>
       </c>
       <c r="E3" t="n">
-        <v>6.866012658799768</v>
+        <v>1.378005361332005</v>
       </c>
     </row>
     <row r="4">
@@ -2474,16 +2474,16 @@
         <v>45986</v>
       </c>
       <c r="B4" t="n">
-        <v>-9.451128181489821</v>
+        <v>-11.75395806199822</v>
       </c>
       <c r="C4" t="n">
-        <v>-25.67869502801068</v>
+        <v>3.59839056319197</v>
       </c>
       <c r="D4" t="n">
-        <v>-22.19612328464922</v>
+        <v>3.110373034136027</v>
       </c>
       <c r="E4" t="n">
-        <v>-31.64725146613904</v>
+        <v>-8.643585027862192</v>
       </c>
     </row>
     <row r="5">
@@ -2491,16 +2491,16 @@
         <v>45987</v>
       </c>
       <c r="B5" t="n">
-        <v>-32.16980026664169</v>
+        <v>12.12332787376954</v>
       </c>
       <c r="C5" t="n">
-        <v>21.65411378184535</v>
+        <v>14.43015533566131</v>
       </c>
       <c r="D5" t="n">
-        <v>18.67699998434134</v>
+        <v>12.44622678597664</v>
       </c>
       <c r="E5" t="n">
-        <v>-13.49280028230034</v>
+        <v>24.56955465974617</v>
       </c>
     </row>
     <row r="6">
@@ -2508,7 +2508,7 @@
         <v>45988</v>
       </c>
       <c r="B6" t="n">
-        <v>29.1860634739287</v>
+        <v>9.335215663285908</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -2519,16 +2519,16 @@
         <v>45989</v>
       </c>
       <c r="B7" t="n">
-        <v>-25.77515005667647</v>
+        <v>-11.75715525797023</v>
       </c>
       <c r="C7" t="n">
-        <v>16.66982850461409</v>
+        <v>-4.367167356686423</v>
       </c>
       <c r="D7" t="n">
-        <v>14.3767386844451</v>
+        <v>-3.766422903567419</v>
       </c>
       <c r="E7" t="n">
-        <v>-11.39841137223137</v>
+        <v>-15.52357816153765</v>
       </c>
     </row>
     <row r="8">
@@ -2536,16 +2536,16 @@
         <v>45992</v>
       </c>
       <c r="B8" t="n">
-        <v>-33.30254982678571</v>
+        <v>-24.59377936118244</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.23243330618152</v>
+        <v>9.120917443954113</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.922853838226976</v>
+        <v>7.856087376360131</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.22540366501268</v>
+        <v>-16.73769198482231</v>
       </c>
     </row>
     <row r="9">
@@ -2553,16 +2553,16 @@
         <v>45993</v>
       </c>
       <c r="B9" t="n">
-        <v>8.581535362813611</v>
+        <v>5.543555683306749</v>
       </c>
       <c r="C9" t="n">
-        <v>50.97124634600823</v>
+        <v>6.982246322334504</v>
       </c>
       <c r="D9" t="n">
-        <v>43.8537781519472</v>
+        <v>6.007266903841094</v>
       </c>
       <c r="E9" t="n">
-        <v>52.43531351476081</v>
+        <v>11.55082258714784</v>
       </c>
     </row>
     <row r="10">
@@ -2570,16 +2570,16 @@
         <v>45994</v>
       </c>
       <c r="B10" t="n">
-        <v>24.92392071508857</v>
+        <v>3.337706564164819</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.048868591937207</v>
+        <v>3.058161092092178</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.755671458386639</v>
+        <v>2.620532212589698</v>
       </c>
       <c r="E10" t="n">
-        <v>23.16824925670193</v>
+        <v>5.958238776754516</v>
       </c>
     </row>
     <row r="11">
@@ -2587,16 +2587,16 @@
         <v>45995</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.642167437168609</v>
+        <v>7.162700134107581</v>
       </c>
       <c r="C11" t="n">
-        <v>27.46605393108348</v>
+        <v>25.27588435461939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.59018631888987</v>
+        <v>21.70908215633376</v>
       </c>
       <c r="E11" t="n">
-        <v>21.94801888172126</v>
+        <v>28.87178229044134</v>
       </c>
     </row>
     <row r="12">
@@ -2604,16 +2604,16 @@
         <v>45996</v>
       </c>
       <c r="B12" t="n">
-        <v>12.0485141006402</v>
+        <v>22.43647836176569</v>
       </c>
       <c r="C12" t="n">
-        <v>18.52110291966346</v>
+        <v>-14.97605055017266</v>
       </c>
       <c r="D12" t="n">
-        <v>15.90886696415003</v>
+        <v>-12.86381253235927</v>
       </c>
       <c r="E12" t="n">
-        <v>27.95738106479023</v>
+        <v>9.572665829406427</v>
       </c>
     </row>
     <row r="13">
@@ -2621,16 +2621,16 @@
         <v>45999</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.09015776810974785</v>
+        <v>26.64045227566248</v>
       </c>
       <c r="C13" t="n">
-        <v>-8.376264043718493</v>
+        <v>-2.020895781405216</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.198576868097708</v>
+        <v>-1.736761585944668</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.288734636207455</v>
+        <v>24.90369068971782</v>
       </c>
     </row>
     <row r="14">
@@ -2638,16 +2638,16 @@
         <v>46000</v>
       </c>
       <c r="B14" t="n">
-        <v>25.91608028551263</v>
+        <v>0.2268790424805047</v>
       </c>
       <c r="C14" t="n">
-        <v>1.827145957084667</v>
+        <v>-6.133095401853097</v>
       </c>
       <c r="D14" t="n">
-        <v>1.571738457707241</v>
+        <v>-5.275780990841374</v>
       </c>
       <c r="E14" t="n">
-        <v>27.48781874321988</v>
+        <v>-5.048901948360869</v>
       </c>
     </row>
     <row r="15">
@@ -2655,16 +2655,16 @@
         <v>46001</v>
       </c>
       <c r="B15" t="n">
-        <v>2.211756287336357</v>
+        <v>6.765929655926357</v>
       </c>
       <c r="C15" t="n">
-        <v>5.47933437090478</v>
+        <v>-5.031619310963833</v>
       </c>
       <c r="D15" t="n">
-        <v>4.685594639049753</v>
+        <v>-4.302735856818739</v>
       </c>
       <c r="E15" t="n">
-        <v>6.897350926386109</v>
+        <v>2.463193799107618</v>
       </c>
     </row>
     <row r="16">
@@ -2672,16 +2672,16 @@
         <v>46002</v>
       </c>
       <c r="B16" t="n">
-        <v>-14.36060671844916</v>
+        <v>-8.155031761019018</v>
       </c>
       <c r="C16" t="n">
-        <v>-28.37754176266981</v>
+        <v>-9.62761939136999</v>
       </c>
       <c r="D16" t="n">
-        <v>-24.17578954052633</v>
+        <v>-8.202095238856696</v>
       </c>
       <c r="E16" t="n">
-        <v>-38.53639625897549</v>
+        <v>-16.35712699987571</v>
       </c>
     </row>
     <row r="17">
@@ -2689,16 +2689,16 @@
         <v>46003</v>
       </c>
       <c r="B17" t="n">
-        <v>-11.62126509580867</v>
+        <v>1.131769105283183</v>
       </c>
       <c r="C17" t="n">
-        <v>16.66737118103219</v>
+        <v>-4.348644389699984</v>
       </c>
       <c r="D17" t="n">
-        <v>14.19707937055553</v>
+        <v>-3.704126396678011</v>
       </c>
       <c r="E17" t="n">
-        <v>2.575814274746866</v>
+        <v>-2.572357291394828</v>
       </c>
     </row>
     <row r="18">
@@ -2706,16 +2706,16 @@
         <v>46006</v>
       </c>
       <c r="B18" t="n">
-        <v>-25.69934616819955</v>
+        <v>-9.905595366783473</v>
       </c>
       <c r="C18" t="n">
-        <v>-41.77046143378811</v>
+        <v>-16.78426266631141</v>
       </c>
       <c r="D18" t="n">
-        <v>-35.54327895999669</v>
+        <v>-14.28204787807301</v>
       </c>
       <c r="E18" t="n">
-        <v>-61.24262512819625</v>
+        <v>-24.18764324485649</v>
       </c>
     </row>
     <row r="19">
@@ -2723,16 +2723,16 @@
         <v>46007</v>
       </c>
       <c r="B19" t="n">
-        <v>5.849157257416664</v>
+        <v>3.535180776098514</v>
       </c>
       <c r="C19" t="n">
-        <v>41.79643736768003</v>
+        <v>13.1383913721761</v>
       </c>
       <c r="D19" t="n">
-        <v>35.5835496064022</v>
+        <v>11.18541748014311</v>
       </c>
       <c r="E19" t="n">
-        <v>41.43270686381886</v>
+        <v>14.72059825624163</v>
       </c>
     </row>
     <row r="20">
@@ -2740,16 +2740,16 @@
         <v>46008</v>
       </c>
       <c r="B20" t="n">
-        <v>34.45188207913588</v>
+        <v>-20.5805731996038</v>
       </c>
       <c r="C20" t="n">
-        <v>-20.82386336840909</v>
+        <v>-14.41459932678299</v>
       </c>
       <c r="D20" t="n">
-        <v>-17.73904367357449</v>
+        <v>-12.27923956621773</v>
       </c>
       <c r="E20" t="n">
-        <v>16.7128384055614</v>
+        <v>-32.85981276582153</v>
       </c>
     </row>
     <row r="21">
@@ -2757,16 +2757,16 @@
         <v>46009</v>
       </c>
       <c r="B21" t="n">
-        <v>9.567153697915273</v>
+        <v>-5.569430197207112</v>
       </c>
       <c r="C21" t="n">
-        <v>65.41229336119522</v>
+        <v>26.32477283179378</v>
       </c>
       <c r="D21" t="n">
-        <v>55.80777524204012</v>
+        <v>22.45949392696338</v>
       </c>
       <c r="E21" t="n">
-        <v>65.3749289399554</v>
+        <v>16.89006372975627</v>
       </c>
     </row>
     <row r="22">
@@ -2774,16 +2774,16 @@
         <v>46010</v>
       </c>
       <c r="B22" t="n">
-        <v>59.04165620227423</v>
+        <v>14.817963524079</v>
       </c>
       <c r="C22" t="n">
-        <v>6.976612293662129</v>
+        <v>-18.385622248451</v>
       </c>
       <c r="D22" t="n">
-        <v>5.958842068382412</v>
+        <v>-15.7034696348232</v>
       </c>
       <c r="E22" t="n">
-        <v>65.00049827065664</v>
+        <v>-0.8855061107441919</v>
       </c>
     </row>
     <row r="23">
@@ -2791,16 +2791,16 @@
         <v>46013</v>
       </c>
       <c r="B23" t="n">
-        <v>14.15947436453098</v>
+        <v>15.2620351069445</v>
       </c>
       <c r="C23" t="n">
-        <v>10.43264423107257</v>
+        <v>3.259417363915418</v>
       </c>
       <c r="D23" t="n">
-        <v>8.87129611485763</v>
+        <v>2.771613404689981</v>
       </c>
       <c r="E23" t="n">
-        <v>23.03077047938861</v>
+        <v>18.03364851163447</v>
       </c>
     </row>
     <row r="24">
@@ -2808,16 +2808,16 @@
         <v>46014</v>
       </c>
       <c r="B24" t="n">
-        <v>-4.460455996461405</v>
+        <v>0.2845258570914666</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.707182455605107</v>
+        <v>8.680187472189573</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.53483335221732</v>
+        <v>7.359833366279102</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.99528934867872</v>
+        <v>7.644359223370569</v>
       </c>
     </row>
     <row r="25">
@@ -2825,16 +2825,16 @@
         <v>46015</v>
       </c>
       <c r="B25" t="n">
-        <v>60.87154161386479</v>
+        <v>-109.0976372388936</v>
       </c>
       <c r="C25" t="n">
-        <v>-3.944824485349727</v>
+        <v>-6.684311842871011</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.349316085370799</v>
+        <v>-5.675252031644601</v>
       </c>
       <c r="E25" t="n">
-        <v>57.52222552849399</v>
+        <v>-114.7728892705382</v>
       </c>
     </row>
     <row r="26">
@@ -2843,10 +2843,10 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>-16.32094283971128</v>
+        <v>9.861750228329129</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.8653834336176</v>
+        <v>8.37800546115804</v>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
@@ -2855,16 +2855,16 @@
         <v>46020</v>
       </c>
       <c r="B27" t="n">
-        <v>-72.59785852878758</v>
+        <v>145.3713739466407</v>
       </c>
       <c r="C27" t="n">
-        <v>4.822874062454048</v>
+        <v>14.24196560768223</v>
       </c>
       <c r="D27" t="n">
-        <v>4.096902873304492</v>
+        <v>12.09816990119116</v>
       </c>
       <c r="E27" t="n">
-        <v>-68.5009556554831</v>
+        <v>157.4695438478319</v>
       </c>
     </row>
     <row r="28">
@@ -2872,16 +2872,16 @@
         <v>46021</v>
       </c>
       <c r="B28" t="n">
-        <v>31.92570548155345</v>
+        <v>-4.586828417894139</v>
       </c>
       <c r="C28" t="n">
-        <v>-28.39437895289348</v>
+        <v>2.834537189240109</v>
       </c>
       <c r="D28" t="n">
-        <v>-24.17365822653965</v>
+        <v>2.413193588660062</v>
       </c>
       <c r="E28" t="n">
-        <v>7.7520472550138</v>
+        <v>-2.173634829234077</v>
       </c>
     </row>
     <row r="29">
@@ -2889,16 +2889,16 @@
         <v>46022</v>
       </c>
       <c r="B29" t="n">
-        <v>89.52537421168199</v>
+        <v>-116.2397302165105</v>
       </c>
       <c r="C29" t="n">
-        <v>-10.4167051017339</v>
+        <v>3.331215146127306</v>
       </c>
       <c r="D29" t="n">
-        <v>-8.869055003604849</v>
+        <v>2.836283649320822</v>
       </c>
       <c r="E29" t="n">
-        <v>80.65631920807715</v>
+        <v>-113.4034465671896</v>
       </c>
     </row>
     <row r="30">
@@ -2906,16 +2906,16 @@
         <v>46024</v>
       </c>
       <c r="B30" t="n">
-        <v>-52.75639441628573</v>
+        <v>96.84551049575157</v>
       </c>
       <c r="C30" t="n">
-        <v>-13.95066509685603</v>
+        <v>-10.47741808322371</v>
       </c>
       <c r="D30" t="n">
-        <v>-11.90431359062721</v>
+        <v>-8.940539366177756</v>
       </c>
       <c r="E30" t="n">
-        <v>-64.66070800691294</v>
+        <v>87.90497112957381</v>
       </c>
     </row>
     <row r="31">
@@ -2923,16 +2923,16 @@
         <v>46027</v>
       </c>
       <c r="B31" t="n">
-        <v>36.68258754445606</v>
+        <v>65.5023729492541</v>
       </c>
       <c r="C31" t="n">
-        <v>15.49858346568271</v>
+        <v>14.3868623500839</v>
       </c>
       <c r="D31" t="n">
-        <v>13.22404732566785</v>
+        <v>12.2754798208907</v>
       </c>
       <c r="E31" t="n">
-        <v>49.9066348701239</v>
+        <v>77.77785277014479</v>
       </c>
     </row>
     <row r="32">
@@ -2940,16 +2940,16 @@
         <v>46028</v>
       </c>
       <c r="B32" t="n">
-        <v>138.4634468831227</v>
+        <v>-1.207296570333256</v>
       </c>
       <c r="C32" t="n">
-        <v>27.74231228612871</v>
+        <v>-32.1196203473778</v>
       </c>
       <c r="D32" t="n">
-        <v>23.73775330378087</v>
+        <v>-27.48320385674493</v>
       </c>
       <c r="E32" t="n">
-        <v>162.2012001869036</v>
+        <v>-28.69050042707819</v>
       </c>
     </row>
     <row r="33">
@@ -2957,16 +2957,16 @@
         <v>46029</v>
       </c>
       <c r="B33" t="n">
-        <v>-124.641732877054</v>
+        <v>22.28086790661291</v>
       </c>
       <c r="C33" t="n">
-        <v>-6.705667028414609</v>
+        <v>-12.41204495998772</v>
       </c>
       <c r="D33" t="n">
-        <v>-5.744596100757825</v>
+        <v>-10.63312341299385</v>
       </c>
       <c r="E33" t="n">
-        <v>-130.3863289778118</v>
+        <v>11.64774449361906</v>
       </c>
     </row>
     <row r="34">
@@ -2974,16 +2974,16 @@
         <v>46030</v>
       </c>
       <c r="B34" t="n">
-        <v>29.64587301550091</v>
+        <v>-70.99117926768395</v>
       </c>
       <c r="C34" t="n">
-        <v>-28.71316525575457</v>
+        <v>42.22778609217357</v>
       </c>
       <c r="D34" t="n">
-        <v>-24.6295807649293</v>
+        <v>36.22215310702828</v>
       </c>
       <c r="E34" t="n">
-        <v>5.016292250571613</v>
+        <v>-34.76902616065566</v>
       </c>
     </row>
     <row r="35">
@@ -2991,16 +2991,16 @@
         <v>46031</v>
       </c>
       <c r="B35" t="n">
-        <v>26.06825616938431</v>
+        <v>38.80140497556249</v>
       </c>
       <c r="C35" t="n">
-        <v>27.06014817941787</v>
+        <v>10.86802008281393</v>
       </c>
       <c r="D35" t="n">
-        <v>23.25354316354547</v>
+        <v>9.339194021495169</v>
       </c>
       <c r="E35" t="n">
-        <v>49.32179933292979</v>
+        <v>48.14059899705766</v>
       </c>
     </row>
     <row r="36">
@@ -3008,16 +3008,16 @@
         <v>46034</v>
       </c>
       <c r="B36" t="n">
-        <v>7.291417144586376</v>
+        <v>-18.672829466027</v>
       </c>
       <c r="C36" t="n">
-        <v>108.4289657591439</v>
+        <v>20.06266596127489</v>
       </c>
       <c r="D36" t="n">
-        <v>92.93645818046106</v>
+        <v>17.19607950739255</v>
       </c>
       <c r="E36" t="n">
-        <v>100.2278753250474</v>
+        <v>-1.476749958634446</v>
       </c>
     </row>
     <row r="37">
@@ -3025,16 +3025,16 @@
         <v>46035</v>
       </c>
       <c r="B37" t="n">
-        <v>-34.42378530966653</v>
+        <v>-9.523331090258125</v>
       </c>
       <c r="C37" t="n">
-        <v>36.42587550995449</v>
+        <v>-32.23842498413205</v>
       </c>
       <c r="D37" t="n">
-        <v>31.29101925088437</v>
+        <v>-27.69386219751916</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.132766058782156</v>
+        <v>-37.21719328777728</v>
       </c>
     </row>
     <row r="38">
@@ -3042,16 +3042,16 @@
         <v>46036</v>
       </c>
       <c r="B38" t="n">
-        <v>33.74052920668419</v>
+        <v>-34.54869505537727</v>
       </c>
       <c r="C38" t="n">
-        <v>-29.29099311331856</v>
+        <v>-10.51204823941589</v>
       </c>
       <c r="D38" t="n">
-        <v>-25.15976044779124</v>
+        <v>-9.029417831485905</v>
       </c>
       <c r="E38" t="n">
-        <v>8.580768758892944</v>
+        <v>-43.57811288686317</v>
       </c>
     </row>
     <row r="39">
@@ -3059,16 +3059,16 @@
         <v>46037</v>
       </c>
       <c r="B39" t="n">
-        <v>-51.60889518312115</v>
+        <v>49.37763224507444</v>
       </c>
       <c r="C39" t="n">
-        <v>10.40563171076155</v>
+        <v>18.01287535648271</v>
       </c>
       <c r="D39" t="n">
-        <v>8.96573471545886</v>
+        <v>15.52031307641109</v>
       </c>
       <c r="E39" t="n">
-        <v>-42.64316046766229</v>
+        <v>64.89794532148552</v>
       </c>
     </row>
     <row r="40">
@@ -3076,16 +3076,16 @@
         <v>46038</v>
       </c>
       <c r="B40" t="n">
-        <v>21.68226126075433</v>
+        <v>-19.83450192521559</v>
       </c>
       <c r="C40" t="n">
-        <v>10.63200375980887</v>
+        <v>-5.040059675891825</v>
       </c>
       <c r="D40" t="n">
-        <v>9.167891489013424</v>
+        <v>-4.346002997233617</v>
       </c>
       <c r="E40" t="n">
-        <v>30.85015274976776</v>
+        <v>-24.18050492244921</v>
       </c>
     </row>
     <row r="41">
@@ -3093,7 +3093,7 @@
         <v>46041</v>
       </c>
       <c r="B41" t="n">
-        <v>-14.01336927118382</v>
+        <v>-74.21496169087823</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -3104,16 +3104,16 @@
         <v>46042</v>
       </c>
       <c r="B42" t="n">
-        <v>-48.35833440870692</v>
+        <v>-26.88062971006866</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.61197540730609</v>
+        <v>-17.54040020632783</v>
       </c>
       <c r="D42" t="n">
-        <v>-6.492643643215702</v>
+        <v>-14.96110560075727</v>
       </c>
       <c r="E42" t="n">
-        <v>-54.85097805192262</v>
+        <v>-41.84173531082594</v>
       </c>
     </row>
     <row r="43">
@@ -3121,16 +3121,16 @@
         <v>46043</v>
       </c>
       <c r="B43" t="n">
-        <v>-13.32753272230821</v>
+        <v>8.236531964494134</v>
       </c>
       <c r="C43" t="n">
-        <v>-3.826255267482338</v>
+        <v>-18.48843336153641</v>
       </c>
       <c r="D43" t="n">
-        <v>-3.275342636091712</v>
+        <v>-15.82642814718063</v>
       </c>
       <c r="E43" t="n">
-        <v>-16.60287535839992</v>
+        <v>-7.589896182686495</v>
       </c>
     </row>
     <row r="44">
@@ -3138,16 +3138,16 @@
         <v>46044</v>
       </c>
       <c r="B44" t="n">
-        <v>-64.99890277850045</v>
+        <v>15.77539688269371</v>
       </c>
       <c r="C44" t="n">
-        <v>22.08146119288358</v>
+        <v>5.223276871851795</v>
       </c>
       <c r="D44" t="n">
-        <v>18.78633758114989</v>
+        <v>4.443829225669385</v>
       </c>
       <c r="E44" t="n">
-        <v>-46.21256519735056</v>
+        <v>20.2192261083631</v>
       </c>
     </row>
     <row r="45">
@@ -3155,16 +3155,16 @@
         <v>46045</v>
       </c>
       <c r="B45" t="n">
-        <v>15.9441294826006</v>
+        <v>-23.00143430641901</v>
       </c>
       <c r="C45" t="n">
-        <v>-38.57055545569438</v>
+        <v>-1.018344647014146</v>
       </c>
       <c r="D45" t="n">
-        <v>-32.615047738622</v>
+        <v>-0.8611065846559666</v>
       </c>
       <c r="E45" t="n">
-        <v>-16.67091825602139</v>
+        <v>-23.86254089107498</v>
       </c>
     </row>
     <row r="46">
@@ -3172,16 +3172,16 @@
         <v>46048</v>
       </c>
       <c r="B46" t="n">
-        <v>-15.58637224289214</v>
+        <v>-40.18716676771601</v>
       </c>
       <c r="C46" t="n">
-        <v>-14.91622993069905</v>
+        <v>-5.525768210714887</v>
       </c>
       <c r="D46" t="n">
-        <v>-12.55680607012295</v>
+        <v>-4.651711600904863</v>
       </c>
       <c r="E46" t="n">
-        <v>-28.14317831301508</v>
+        <v>-44.83887836862087</v>
       </c>
     </row>
     <row r="47">
@@ -3189,16 +3189,16 @@
         <v>46049</v>
       </c>
       <c r="B47" t="n">
-        <v>13.18049220388593</v>
+        <v>10.64901203550471</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7647990435361862</v>
+        <v>-14.7893004116836</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6351623980866924</v>
+        <v>-12.2824519655208</v>
       </c>
       <c r="E47" t="n">
-        <v>13.81565460197262</v>
+        <v>-1.633439930016092</v>
       </c>
     </row>
     <row r="48">
@@ -3206,16 +3206,16 @@
         <v>46050</v>
       </c>
       <c r="B48" t="n">
-        <v>17.55876716219791</v>
+        <v>10.20647380687433</v>
       </c>
       <c r="C48" t="n">
-        <v>-8.16384734144458</v>
+        <v>-16.1899954086507</v>
       </c>
       <c r="D48" t="n">
-        <v>-6.830528230793657</v>
+        <v>-13.54584622544403</v>
       </c>
       <c r="E48" t="n">
-        <v>10.72823893140425</v>
+        <v>-3.339372418569699</v>
       </c>
     </row>
     <row r="49">
@@ -3223,16 +3223,16 @@
         <v>46051</v>
       </c>
       <c r="B49" t="n">
-        <v>30.06789615715979</v>
+        <v>-26.44484636595462</v>
       </c>
       <c r="C49" t="n">
-        <v>-35.9264110831964</v>
+        <v>-22.09365641560089</v>
       </c>
       <c r="D49" t="n">
-        <v>-30.01621779864349</v>
+        <v>-18.45906626752518</v>
       </c>
       <c r="E49" t="n">
-        <v>0.05167835851630187</v>
+        <v>-44.9039126334798</v>
       </c>
     </row>
     <row r="50">
@@ -3240,16 +3240,16 @@
         <v>46052</v>
       </c>
       <c r="B50" t="n">
-        <v>-65.80821629854472</v>
+        <v>-14.36166372529306</v>
       </c>
       <c r="C50" t="n">
-        <v>-105.5512709401441</v>
+        <v>27.34259093925812</v>
       </c>
       <c r="D50" t="n">
-        <v>-89.08783840322766</v>
+        <v>23.07781139370199</v>
       </c>
       <c r="E50" t="n">
-        <v>-154.8960547017724</v>
+        <v>8.716147668408933</v>
       </c>
     </row>
   </sheetData>
